--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92560250995</v>
+        <v>46157.93064643316</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93064643316</v>
+        <v>46157.93148999771</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93148999771</v>
+        <v>46157.93391938263</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93391938263</v>
+        <v>46157.93705516739</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93705516739</v>
+        <v>46158.28209163223</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28209163223</v>
+        <v>46158.29663692165</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29663692165</v>
+        <v>46158.29802280872</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29802280872</v>
+        <v>46158.33379185544</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33379185544</v>
+        <v>46158.3684560956</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3684560956</v>
+        <v>46158.37280062628</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
